--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_function/lang_function__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_function/lang_function__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Resonators</t>
+          <t>Resonator</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Resonance Terminal</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Trao đổi chung</t>
+          <t>Đổi chung</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Thư viện</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bản đồ</t>
+          <t>Bản Đồ</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Resonance Record</t>
+          <t>Biên Bản Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Công cụ thám hiểm</t>
+          <t>Dụng Cụ Thám Hiểm</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Phe phái</t>
+          <t>Lực lượng</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Star Align</t>
+          <t>Sao Đồng Tâm</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Ngân Hàng Dữ Liệu</t>
+          <t>Cơ sở dữ liệu</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Thư viện</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Điều Phối cho phép bạn cộng hưởng với Resonators và Weapons khác nhau. Đây là cách hiệu quả để thu thập vũ khí mạnh và gặp gỡ đồng minh đáng tin cậy.</t>
+          <t>Điều chế giúp bạn cộng hưởng với nhiều Resonator và Vũ khí khác nhau. Đây là cách hiệu quả để thu thập vũ khí mạnh và gặp gỡ đồng minh đáng tin cậy.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Chơi cùng nhau</t>
+          <t>Hợp tác</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Chế độ Co-op sẽ giúp bạn gặp gỡ các Rover khác. Kindness có thể dẫn bạn đến những tình bạn quý giá.</t>
+          <t>Chế độ Hợp tác cho phép bạn gặp gỡ các Vận Mệnh Giả khác. Sự tử tế có thể mang đến những tình bạn quý giá.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Resonance Record</t>
+          <t>Biên Bản Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Resonance Terminal đã được lắp đặt module của Tacet Discord, Mutant Organism và Tacet Fields. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng trong hoang dã.</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng được lắp đặt mô-đun của Tacet Discord, Sinh Vật Đột Biến và Tổ Tacet. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Bản Ghi Đơn</t>
+          <t>Kỷ Lục Solo</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Bạn có thể trải nghiệm câu chuyện đặc biệt của Resonators trong Solo Record.</t>
+          <t>Trải nghiệm câu chuyện đặc biệt của Resonator trong Bản Ghi Đơn.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Công cụ thám hiểm</t>
+          <t>Dụng Cụ Thám Hiểm</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Công cụ khám phá đã được cài đặt trong Resonance Terminal. Chúng linh hoạt để xử lý nhiều tình huống khác nhau.</t>
+          <t>Công cụ thám hiểm tích hợp trong Thiết bị đầu cuối Cộng Hưởng. Linh hoạt xử lý nhiều tình huống.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Trạm Tiến Triển</t>
+          <t>Căn Cứ Đang Phát Triển</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Pioneer Association đã tạo ra Ambience này mô phỏng từ giếng của Trạm Nghiên cứu Zero Point. Nó được sử dụng để huấn luyện và thử nghiệm Resonators trước khi họ tiến vào Trạm Nghiên cứu Zero Point.</t>
+          <t>Hiệp Hội Tiên Phong tạo ra Bầu Không Khí này dựa trên giếng của Trạm Nghiên Cứu Điểm Không. Nó được dùng để huấn luyện và thử nghiệm Resonator trước khi họ tiến vào Trạm Nghiên Cứu Điểm Không.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Trung tâm thí nghiệm ngầm quy mô lớn được xây dựng trước Thương Khốc. Giếng bên dưới đạt độ sâu tới ranh giới Moho. Những bí mật và tri thức chưa biết đang chờ đợ bạn tại đây.</t>
+          <t>Trung tâm thí nghiệm ngầm quy mô lớn được xây dựng trước Đại Than Vãn. Giếng bên dưới đạt độ sâu tới ranh giới Moho. Những bí mật và tri thức chưa biết đang chờ bạn ở đó.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách Tacet Field và kẻ địch Overlord Class để thu thập tài nguyên. Lần đầu hoàn thành sẽ nhận được mẫu vật để đổi lấy vật liệu hiếm tại Interference Exchange.</t>
+          <t>Hoàn thành thử thách Tổ Tacet và kẻ địch Hạng Overlord sẽ giúp bạn thu thập tài nguyên. Lần đầu vượt qua sẽ nhận mẫu vật để đổi nguyên liệu hiếm tại Trao Đổi Nhiễu Loạn.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Kỹ năng mạnh được thực hiện bởi 2 Resonators. Khi Concerto Vibrancy được nạp đầy, việc chuyển đổi Resonators sẽ tiêu hao toàn bộ và kích hoạt Concerto Effect dựa trên thuộc tính tấn công của nhân vật được chuyển đổi.</t>
+          <t>Kỹ năng mạnh được thực hiện bởi 2 Resonator. Khi Năng Lượng Giao Hưởng được nạp đầy, chuyển đổi Resonator sẽ tiêu hao toàn bộ và kích hoạt Hiệu Ứng Giao Hưởng dựa trên thuộc tính tấn công của nhân vật được chuyển đến.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Star Align</t>
+          <t>Sao Đồng Tâm</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Nâng Sao cho Rover sẽ nhận được EXP Nhiệm Vụ để đổi lấy phần thưởng.</t>
+          <t>Hoàn thành Nhiệm Vụ Nâng Sao cho Rover sẽ nhận Điểm Kinh Nghiệm Nhiệm Vụ để đổi phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Không khí của Resonators tinh thông vũ khí. Những giai điệu trong lưỡi kiếm gãy của họ có thể được dùng để tăng cường vũ khí.</t>
+          <t>Bối cảnh của Resonator tinh thông vũ khí. Giai điệu trong lưỡi kiếm gãy của họ có thể tăng cường vũ khí.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Ambience của những Resonators tinh thông kỹ thuật chiến đấu. Những giai điệu trong ký ức tan vỡ của họ có thể được dùng để nâng cao kỹ năng chiến đấu.</t>
+          <t>Bối cảnh của Resonator tinh thông kỹ thuật chiến đấu. Giai điệu trong ký ức tan vỡ của họ có thể tăng cường kỹ năng chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Chế độ Co-op sẽ giúp bạn gặp gỡ các Rover khác. Kindness có thể dẫn bạn đến những tình bạn quý giá.</t>
+          <t>Chế độ Hợp tác cho phép bạn gặp gỡ các Vận Mệnh Giả khác. Sự tử tế có thể mang đến những tình bạn quý giá.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Resonance Record</t>
+          <t>Biên Bản Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Resonance Terminal đã được lắp đặt module của Tacet Discord, Mutant Organism và Tacet Fields. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng trong hoang dã.</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng được lắp đặt mô-đun của Tacet Discord, Sinh Vật Đột Biến và Tổ Tacet. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Resonance Record</t>
+          <t>Biên Bản Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Resonance Terminal đã được lắp đặt module của Tacet Discord, Mutant Organism và Tacet Fields. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng trong hoang dã.</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng được lắp đặt mô-đun của Tacet Discord, Sinh Vật Đột Biến và Tổ Tacet. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Resonance Record</t>
+          <t>Biên Bản Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Resonance Terminal đã được lắp đặt module của Tacet Discord, Mutant Organism và Tacet Fields. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng trong hoang dã.</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng được lắp đặt mô-đun của Tacet Discord, Sinh Vật Đột Biến và Tổ Tacet. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Resonance Record</t>
+          <t>Biên Bản Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Resonance Terminal đã được lắp đặt module của Tacet Discord, Mutant Organism và Tacet Fields. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng trong hoang dã.</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng được lắp đặt mô-đun của Tacet Discord, Sinh Vật Đột Biến và Tổ Tacet. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng ngoài hoang dã.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Resonance Record</t>
+          <t>Biên Bản Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Resonance Terminal đã được lắp đặt module của Tacet Discord, Mutant Organism và Tacet Fields. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng trong hoang dã.</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng được lắp đặt mô-đun của Tacet Discord, Sinh Vật Đột Biến và Tổ Tacet. Sử dụng chúng sẽ giúp bạn nhanh chóng xác định vị trí của chúng ngoài hoang dã.</t>
         </is>
       </c>
     </row>
